--- a/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +30,6 @@
       <b val="1"/>
       <color rgb="00111827"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="009CA3AF"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -87,19 +82,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.5" customWidth="1" min="1" max="1"/>
@@ -479,82 +473,68 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>※ 예시값 — 표기 금액·요율·상호는 전부 예시이며 실제 거래 기록이 아니다. 수수료율은 미확정이고 할인율 0.11%는 예정값이다.</t>
-        </is>
-      </c>
-    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>검색대상기간</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>일주일 (2026-08-21 ~ 2026-08-27)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>투자실행금</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="5" t="n">
         <v>1250800000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>투자수익</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <v>1375880</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Ty수익율 (투자실행금액 대비)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.0355</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ty수익율 (투자자산 대비)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.0224</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>※ Ty수익율 = 할인율 × (365 ÷ W금융일수). 투자자산 대비 수익율의 분모는 기간 투자실행금 합 + 기간 순현금 합(PSC).</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.0355</v>
+        <v>0.1295</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.0224</v>
+        <v>0.0815</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1250800000</v>
+        <v>3511071647</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1375880</v>
+        <v>3862175</v>
       </c>
     </row>
     <row r="7">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.0815</v>
+        <v>0.107</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>3862175</v>
+        <v>3866428</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.1295</v>
+        <v>0.1297</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.107</v>
+        <v>0.1072</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3511071647</v>
+        <v>200353526</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>3866428</v>
+        <v>106120</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.1297</v>
+        <v>0.06909999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.1072</v>
+        <v>0.0407</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>200353526</v>
+        <v>179970919</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>106120</v>
+        <v>61175</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0399</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.0407</v>
+        <v>0.0224</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>61175</v>
+        <v>198184</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.0399</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.0319</v>
+        <v>0.1034</v>
       </c>
     </row>
   </sheetData>
